--- a/trust/v1.6.0/CodeSystem-RefMartCountryList.xlsx
+++ b/trust/v1.6.0/CodeSystem-RefMartCountryList.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T08:19:48+00:00</t>
+    <t>2026-07-06T11:47:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
